--- a/docs/formalml-content-metrics.xlsx
+++ b/docs/formalml-content-metrics.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R63"/>
+  <dimension ref="A1:R64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5113,6 +5113,80 @@
       <c r="R63" t="inlineStr">
         <is>
           <t>Motivation and the task-distribution structure, Gradient-based meta-learning: MAML, First-order approximations and implicit gradients, Bayesian meta-learning: Neural Processes, Metric-learning meta-learning: Prototypical Networks, The hierarchical-Bayes unifying view, PAC-Bayes generalization theory for meta-learning, Convergence guarantees for MAML, Comparative benchmarks and ablations, Computational notes, Connections and limits</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>bayesian-ml</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Reversible-Jump MCMC</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>advanced</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>14873</v>
+      </c>
+      <c r="E64" t="n">
+        <v>13</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>3</v>
+      </c>
+      <c r="L64" t="n">
+        <v>9</v>
+      </c>
+      <c r="M64" t="n">
+        <v>110</v>
+      </c>
+      <c r="N64" t="n">
+        <v>1005</v>
+      </c>
+      <c r="O64" t="n">
+        <v>19</v>
+      </c>
+      <c r="P64" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Overview and motivation; Bayesian model selection at a glance — what RJ-MCMC computes; The trans-dimensional state space; Standard MH refresher and where it stops short; The dimension-matching auxiliary-variable construction; Reversibility of the bijection and the involution shortcut; Detailed balance with the Jacobian correction — the master acceptance ratio; The move catalog — split/merge, birth/death, and RJ-MH; Worked example A — Linear-regression variable selection (Kuo–Mallick); Worked example B — Univariate Gaussian-mixture order estimation (Richardson–Green on Galaxy data); Diagnostics for trans-dimensional chains; Computational notes; Connections and limits</t>
         </is>
       </c>
     </row>
@@ -5562,19 +5636,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>8283</v>
+        <v>9015</v>
       </c>
       <c r="D11" t="n">
         <v>2764</v>
       </c>
       <c r="E11" t="n">
-        <v>11882</v>
+        <v>14873</v>
       </c>
       <c r="F11" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
@@ -5583,10 +5657,10 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>

--- a/docs/formalml-content-metrics.xlsx
+++ b/docs/formalml-content-metrics.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R64"/>
+  <dimension ref="A1:R65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5187,6 +5187,80 @@
       <c r="R64" t="inlineStr">
         <is>
           <t>Overview and motivation; Bayesian model selection at a glance — what RJ-MCMC computes; The trans-dimensional state space; Standard MH refresher and where it stops short; The dimension-matching auxiliary-variable construction; Reversibility of the bijection and the involution shortcut; Detailed balance with the Jacobian correction — the master acceptance ratio; The move catalog — split/merge, birth/death, and RJ-MH; Worked example A — Linear-regression variable selection (Kuo–Mallick); Worked example B — Univariate Gaussian-mixture order estimation (Richardson–Green on Galaxy data); Diagnostics for trans-dimensional chains; Computational notes; Connections and limits</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>unsupervised</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Representation Learning</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>advanced</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>7980</v>
+      </c>
+      <c r="E65" t="n">
+        <v>13</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>42</v>
+      </c>
+      <c r="M65" t="n">
+        <v>60</v>
+      </c>
+      <c r="N65" t="n">
+        <v>859</v>
+      </c>
+      <c r="O65" t="n">
+        <v>45</v>
+      </c>
+      <c r="P65" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>What is a representation, and what makes one good?; Sufficient statistics as the limit point of "good representation"; The autoencoder family; The variational autoencoder; The contrastive principle and the InfoNCE bound; SimCLR and the design space of contrastive methods; The information bottleneck perspective; Self-supervised pretext tasks beyond contrastive; Evaluating representations; Identifiability and what self-supervision cannot give you; Computational considerations; The geometry of learned representations; Connections, limits, and forward pointers</t>
         </is>
       </c>
     </row>
@@ -5716,10 +5790,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>10197.5</v>
+        <v>9458.333333333334</v>
       </c>
       <c r="D13" t="n">
         <v>6346</v>
@@ -5728,7 +5802,7 @@
         <v>14049</v>
       </c>
       <c r="F13" t="n">
-        <v>12</v>
+        <v>12.33333333333333</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -5737,7 +5811,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -5800,7 +5874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7159,6 +7233,33 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Representation Learning</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>unsupervised</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Missing code section</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Brief §11.4 explicitly addresses computational considerations in prose; code lives in the executed companion notebook at notebooks/representation-learning/01_representation_learning.ipynb (NumPy/SciPy for §3.2 Baldi-Hornik, §3.4 Tweedie, §5.3 InfoNCE bound, §7.2 Gaussian IB; PyTorch for §4 VAE, §5.5 contrastive trajectory, §6.2 SimCLR projection head, §12.3 neural-collapse classifier). No dedicated MDX code section by design — the in-browser TS shared module (src/components/viz/shared/representation-learning.ts) plus the four precompute scripts cover the computational surface.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/formalml-content-metrics.xlsx
+++ b/docs/formalml-content-metrics.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Topic Detail" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domain Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gap Analysis" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Topic Detail" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Domain Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Gap Analysis" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R65"/>
+  <dimension ref="A1:R66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5261,6 +5261,80 @@
       <c r="R65" t="inlineStr">
         <is>
           <t>What is a representation, and what makes one good?; Sufficient statistics as the limit point of "good representation"; The autoencoder family; The variational autoencoder; The contrastive principle and the InfoNCE bound; SimCLR and the design space of contrastive methods; The information bottleneck perspective; Self-supervised pretext tasks beyond contrastive; Evaluating representations; Identifiability and what self-supervision cannot give you; Computational considerations; The geometry of learned representations; Connections, limits, and forward pointers</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>bayesian-ml</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Bayesian Inference</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>foundational</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>9991</v>
+      </c>
+      <c r="E66" t="n">
+        <v>13</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>19</v>
+      </c>
+      <c r="M66" t="n">
+        <v>62</v>
+      </c>
+      <c r="N66" t="n">
+        <v>727</v>
+      </c>
+      <c r="O66" t="n">
+        <v>30</v>
+      </c>
+      <c r="P66" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>1. Why Bayesian inference?; 2. The prior–likelihood–posterior cycle; 3. Choosing a prior; 4. Conjugate families; 5. Point estimates from a posterior; 6. The posterior predictive distribution; 7. Bayesian decision theory; 8. Sequential updating and exchangeability; 9. Hierarchical Bayes and partial pooling; 10. Bayesian model comparison; 11. Computational reality; 12. The frequentist–Bayesian dialogue; 13. Connections and limits</t>
         </is>
       </c>
     </row>
@@ -5710,10 +5784,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>9015</v>
+        <v>9113</v>
       </c>
       <c r="D11" t="n">
         <v>2764</v>
@@ -5722,7 +5796,7 @@
         <v>14873</v>
       </c>
       <c r="F11" t="n">
-        <v>9.800000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
@@ -5731,10 +5805,10 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -5874,7 +5948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7260,6 +7334,33 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Bayesian Inference</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>bayesian-ml</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Missing code section</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Umbrella topic by design — code lives in the executed companion notebook at notebooks/bayesian-inference/01_bayesian_inference.ipynb (NumPy/SciPy/matplotlib only, no MCMC libraries). The in-browser TS shared module (src/components/viz/shared/bayesian-inference.ts) covers Beta/Normal/Bayes-factor/EB primitives for the 11 interactive viz. No dedicated MDX code section by design — the brief explicitly forward-points algorithmic content to the 13 T5 leaves.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/formalml-content-metrics.xlsx
+++ b/docs/formalml-content-metrics.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Topic Detail" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Domain Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Gap Analysis" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Topic Detail" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domain Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gap Analysis" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R66"/>
+  <dimension ref="A1:R67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5335,6 +5335,80 @@
       <c r="R66" t="inlineStr">
         <is>
           <t>1. Why Bayesian inference?; 2. The prior–likelihood–posterior cycle; 3. Choosing a prior; 4. Conjugate families; 5. Point estimates from a posterior; 6. The posterior predictive distribution; 7. Bayesian decision theory; 8. Sequential updating and exchangeability; 9. Hierarchical Bayes and partial pooling; 10. Bayesian model comparison; 11. Computational reality; 12. The frequentist–Bayesian dialogue; 13. Connections and limits</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>learning-theory</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Selective Inference</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>advanced</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>14560</v>
+      </c>
+      <c r="E67" t="n">
+        <v>14</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>27</v>
+      </c>
+      <c r="M67" t="n">
+        <v>79</v>
+      </c>
+      <c r="N67" t="n">
+        <v>1291</v>
+      </c>
+      <c r="O67" t="n">
+        <v>35</v>
+      </c>
+      <c r="P67" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>1. Motivation; 2. The selection-event framework; 3. Polyhedral selection events for the lasso; 4. Conditional z-tests and confidence intervals via the truncated-Gaussian pivot; 5. The debiased lasso; 6. FDR, the Benjamini–Hochberg procedure, and Storey's adaptive variant; 7. The knockoff filter — fixed-X construction; 8. Model-X knockoffs; 9. Constructing knockoffs in practice; 10. Online FDR procedures; 11. Wealth processes and supermartingale FDR proofs; 12. ML applications; 13. Computational notes; 14. Connections and limits</t>
         </is>
       </c>
     </row>
@@ -5904,16 +5978,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14" t="n">
-        <v>8116.5</v>
+        <v>8832.4</v>
       </c>
       <c r="D14" t="n">
         <v>4419</v>
       </c>
       <c r="E14" t="n">
-        <v>13112</v>
+        <v>14560</v>
       </c>
       <c r="F14" t="n">
         <v>13.9</v>
@@ -5925,7 +5999,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>

--- a/docs/formalml-content-metrics.xlsx
+++ b/docs/formalml-content-metrics.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Topic Detail" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domain Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gap Analysis" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Topic Detail" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Domain Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Gap Analysis" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R67"/>
+  <dimension ref="A1:R68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5409,6 +5409,80 @@
       <c r="R67" t="inlineStr">
         <is>
           <t>1. Motivation; 2. The selection-event framework; 3. Polyhedral selection events for the lasso; 4. Conditional z-tests and confidence intervals via the truncated-Gaussian pivot; 5. The debiased lasso; 6. FDR, the Benjamini–Hochberg procedure, and Storey's adaptive variant; 7. The knockoff filter — fixed-X construction; 8. Model-X knockoffs; 9. Constructing knockoffs in practice; 10. Online FDR procedures; 11. Wealth processes and supermartingale FDR proofs; 12. ML applications; 13. Computational notes; 14. Connections and limits</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>learning-theory</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>The Information Bottleneck</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>advanced</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>7965</v>
+      </c>
+      <c r="E68" t="n">
+        <v>12</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>13</v>
+      </c>
+      <c r="M68" t="n">
+        <v>97</v>
+      </c>
+      <c r="N68" t="n">
+        <v>857</v>
+      </c>
+      <c r="O68" t="n">
+        <v>34</v>
+      </c>
+      <c r="P68" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>1. What problem does the information bottleneck solve?, 2. The information bottleneck Lagrangian, 3. The IB fixed-point equations, 4. Convergence of the IB updates, 5. The discrete IB in practice, 6. The Gaussian information bottleneck, 7. Phase transitions on the Gaussian IB curve, 8. Variational IB and the deep-learning lift, 9. The fitting and compression controversy, 10. IB beyond compression-vs-prediction, 11. Connections to other principles, 12. Computational notes and honest limits</t>
         </is>
       </c>
     </row>
@@ -5978,10 +6052,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C14" t="n">
-        <v>8832.4</v>
+        <v>8746</v>
       </c>
       <c r="D14" t="n">
         <v>4419</v>
@@ -5990,7 +6064,7 @@
         <v>14560</v>
       </c>
       <c r="F14" t="n">
-        <v>13.9</v>
+        <v>13.7</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>

--- a/docs/formalml-content-metrics.xlsx
+++ b/docs/formalml-content-metrics.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Topic Detail" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Domain Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Gap Analysis" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Topic Detail" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domain Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gap Analysis" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R68"/>
+  <dimension ref="A1:R69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5483,6 +5483,80 @@
       <c r="R68" t="inlineStr">
         <is>
           <t>1. What problem does the information bottleneck solve?, 2. The information bottleneck Lagrangian, 3. The IB fixed-point equations, 4. Convergence of the IB updates, 5. The discrete IB in practice, 6. The Gaussian information bottleneck, 7. Phase transitions on the Gaussian IB curve, 8. Variational IB and the deep-learning lift, 9. The fitting and compression controversy, 10. IB beyond compression-vs-prediction, 11. Connections to other principles, 12. Computational notes and honest limits</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>learning-theory</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Generalized Method of Moments</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>advanced</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>8514</v>
+      </c>
+      <c r="E69" t="n">
+        <v>13</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Yes (14)</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>19</v>
+      </c>
+      <c r="M69" t="n">
+        <v>65</v>
+      </c>
+      <c r="N69" t="n">
+        <v>782</v>
+      </c>
+      <c r="O69" t="n">
+        <v>27</v>
+      </c>
+      <c r="P69" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>§1 Introduction; §2 Classical MoM; §3 GMM framework; §4 Consistency; §5 Asymptotic normality; §6 Efficient weighting + Hansen bound; §7 Two-step feasible; §8 Hansen J-statistic; §9 Linear GMM + 2SLS; §10 Modern GMM (CUE/EL/GEL); §11 GMM and MLE; §12 GMM in modern causal inference; §13 Computational notes + connections</t>
         </is>
       </c>
     </row>
@@ -6052,10 +6126,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C14" t="n">
-        <v>8746</v>
+        <v>8725</v>
       </c>
       <c r="D14" t="n">
         <v>4419</v>
@@ -6064,7 +6138,7 @@
         <v>14560</v>
       </c>
       <c r="F14" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
